--- a/ONCHO/Entomological survey Survey/Nigeria/2025/kaduna/ng_oncho_2508_1_com_kad.xlsx
+++ b/ONCHO/Entomological survey Survey/Nigeria/2025/kaduna/ng_oncho_2508_1_com_kad.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Entomological survey Survey\Nigeria\2025\kaduna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5AA867A-9059-4711-B38E-DD455DED97D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B27878-A4E7-4BE1-9354-53A16E1F737A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -1714,7 +1714,7 @@
         <v>73</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1728,7 +1728,7 @@
         <v>74</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1742,7 +1742,7 @@
         <v>75</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1756,7 +1756,7 @@
         <v>76</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1770,7 +1770,7 @@
         <v>77</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1784,7 +1784,7 @@
         <v>78</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1798,7 +1798,7 @@
         <v>79</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1812,7 +1812,7 @@
         <v>80</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1826,7 +1826,7 @@
         <v>81</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1840,7 +1840,7 @@
         <v>82</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1854,7 +1854,7 @@
         <v>83</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1868,7 +1868,7 @@
         <v>84</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1882,7 +1882,7 @@
         <v>85</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1896,7 +1896,7 @@
         <v>86</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="19" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1910,7 +1910,7 @@
         <v>87</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:5" s="19" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1924,7 +1924,7 @@
         <v>88</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:5" s="19" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1938,7 +1938,7 @@
         <v>89</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="19" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1952,7 +1952,7 @@
         <v>90</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="19" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1966,7 +1966,7 @@
         <v>91</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="19" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1980,7 +1980,7 @@
         <v>92</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:5" s="19" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
